--- a/docs/camera-spec-sheet-EN.xlsx
+++ b/docs/camera-spec-sheet-EN.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Front tip of a handheld pen-type scalp scanner, facing the scalp. Module includes LED ring (white + 365nm UV) and protective front window.</t>
+          <t>Front tip of a handheld scalp scanner, facing the scalp. Module includes LED ring (white + 365nm UV) and protective front window.</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>

--- a/docs/camera-spec-sheet-EN.xlsx
+++ b/docs/camera-spec-sheet-EN.xlsx
@@ -1168,7 +1168,7 @@
       <c r="Y29" s="7" t="n"/>
       <c r="Z29" s="7" t="n"/>
     </row>
-    <row r="30" ht="68.5" customFormat="1" customHeight="1" s="1">
+    <row r="30" ht="50" customFormat="1" customHeight="1" s="1">
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="9" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Auto-Focus (VCM) - REQUIRED. White mode: continuous AF. UV mode: VCM locked at last white-light focus position.</t>
+          <t>Auto-Focus (VCM) - REQUIRED. Continuous AF in both white-light and UV modes.</t>
         </is>
       </c>
       <c r="D30" s="8" t="n"/>
@@ -1328,7 +1328,7 @@
       <c r="Y33" s="7" t="n"/>
       <c r="Z33" s="7" t="n"/>
     </row>
-    <row r="34" ht="118.5" customFormat="1" customHeight="1" s="1">
+    <row r="34" ht="62" customFormat="1" customHeight="1" s="1">
       <c r="A34" s="7" t="n"/>
       <c r="B34" s="9" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>AE, AWB, AF, center ROI crop, mirror/flip. Separate IQ per light mode: White = auto AE/AWB, continuous AF; UV = AWB off, fixed exposure/gain, AF locked, drop 1-2 mixed-light frames after switching.</t>
+          <t>AE, AWB, AF, center ROI crop, mirror/flip. Same ISP settings in white-light and UV modes (auto AE / auto AWB / continuous AF).</t>
         </is>
       </c>
       <c r="D34" s="8" t="n"/>

--- a/docs/camera-spec-sheet-EN.xlsx
+++ b/docs/camera-spec-sheet-EN.xlsx
@@ -1524,7 +1524,7 @@
       <c r="Y38" s="7" t="n"/>
       <c r="Z38" s="7" t="n"/>
     </row>
-    <row r="39" ht="68.5" customFormat="1" customHeight="1" s="1">
+    <row r="39" ht="62" customFormat="1" customHeight="1" s="1">
       <c r="A39" s="7" t="n"/>
       <c r="B39" s="9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>RoHS. Final product certifications (KC / CE / FCC) TBD. UV LED: IEC 62471 photobiological safety.</t>
+          <t>KC certification (Korea) for the final product - camera module must support KC EMC compliance. RoHS. UV LED: IEC 62471 photobiological safety.</t>
         </is>
       </c>
       <c r="D39" s="16" t="n"/>

--- a/docs/camera-spec-sheet-EN.xlsx
+++ b/docs/camera-spec-sheet-EN.xlsx
@@ -1048,7 +1048,7 @@
       <c r="Y26" s="7" t="n"/>
       <c r="Z26" s="7" t="n"/>
     </row>
-    <row r="27" ht="106" customFormat="1" customHeight="1" s="1">
+    <row r="27" ht="110" customFormat="1" customHeight="1" s="1">
       <c r="A27" s="7" t="n"/>
       <c r="B27" s="9" t="inlineStr">
         <is>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Macro: object field 6.0 x 6.0 mm (square) at 20 mm camera-module-to-subject distance (from outer surface of front window, TBC). Optical magnification approx. 0.52x.</t>
+          <t>Macro: object field &gt;= 6.0 x 6.0 mm (square) within the sensor center 2240x2240 px, at 20 mm camera-module-to-subject distance (from outer surface of front window, TBC). Optical magnification approx. 0.50x, so that &gt;= 6.0 mm is kept over the full AF range and manufacturing tolerances. Final value proposed by supplier.</t>
         </is>
       </c>
       <c r="D27" s="8" t="n"/>

--- a/docs/camera-spec-sheet-EN.xlsx
+++ b/docs/camera-spec-sheet-EN.xlsx
@@ -1168,7 +1168,7 @@
       <c r="Y29" s="7" t="n"/>
       <c r="Z29" s="7" t="n"/>
     </row>
-    <row r="30" ht="50" customFormat="1" customHeight="1" s="1">
+    <row r="30" ht="140" customFormat="1" customHeight="1" s="1">
       <c r="A30" s="7" t="n"/>
       <c r="B30" s="9" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Auto-Focus (VCM) - REQUIRED. Continuous AF in both white-light and UV modes.</t>
+          <t>Auto-Focus (VCM) - REQUIRED. Continuous AF in both white-light and UV modes. AF range: covers subject distance 20 mm +/-0.5 mm or more (hand shake / pressing force). AF speed: focus within 1 s (target, TBD). AF tuning (IQ file for RV1106 ISP) and VCM driver to be provided by supplier. VCM driver IC: I2C control (e.g., DW9714 type) - please share the model.</t>
         </is>
       </c>
       <c r="D30" s="8" t="n"/>
